--- a/jira_export_2026-09-28.xlsx
+++ b/jira_export_2026-09-28.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>50,426 €</t>
+          <t>51,704 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -763,14 +763,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>12,862 €</t>
+          <t>13,101 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>37,564 €</t>
+          <t>38,602 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>415 h</t>
+          <t>420 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>1470.38</v>
       </c>
       <c r="O17" s="16" t="n">
-        <v>1351.16</v>
+        <v>1390.9</v>
       </c>
       <c r="P17" s="12" t="n">
-        <v>284.45</v>
+        <v>278.18</v>
       </c>
     </row>
     <row r="18">
@@ -4168,7 +4168,7 @@
         <v>3</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
         <v>0</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0</v>
+        <v>908.01</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>0</v>
+        <v>201.78</v>
       </c>
     </row>
     <row r="49">
@@ -5308,7 +5308,7 @@
         <v>3</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
@@ -5324,10 +5324,10 @@
         <v>0</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>798.6</v>
+        <v>998.25</v>
       </c>
       <c r="P64" s="15" t="n">
-        <v>99.83</v>
+        <v>95.06999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -8196,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="O104" s="15" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="P104" s="15" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
     </row>
     <row r="105">
@@ -11422,7 +11422,7 @@
         <v>18</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L150" s="14" t="inlineStr">
         <is>
@@ -13452,10 +13452,10 @@
         <v>48185.576</v>
       </c>
       <c r="O183" s="18" t="n">
-        <v>50426.358</v>
+        <v>51703.75799999999</v>
       </c>
       <c r="P183" s="18" t="n">
-        <v>182.32</v>
+        <v>183.62</v>
       </c>
     </row>
   </sheetData>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>141.42</v>
+        <v>144.42</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>47.67</v>
@@ -14891,7 +14891,7 @@
         <v>19.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>208.33</v>
+        <v>211.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>30.67</v>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.4%</t>
         </is>
       </c>
     </row>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -14921,7 +14921,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>66.5</v>
+        <v>68.5</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>7.5</v>
@@ -14931,7 +14931,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
     </row>
@@ -15028,16 +15028,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>402170</v>
+        <v>400892</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>173486</v>
+        <v>173509</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>228683</v>
+        <v>227383</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>159007</v>
+        <v>157707</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>16523</v>
@@ -15053,10 +15053,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>177993</v>
+        <v>177754</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>52129</v>
+        <v>51890</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>125864</v>
@@ -15078,16 +15078,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>224177</v>
+        <v>223139</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>121357</v>
+        <v>121619</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>102820</v>
+        <v>101520</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>52538</v>
+        <v>51238</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>7348</v>

--- a/jira_export_2026-09-28.xlsx
+++ b/jira_export_2026-09-28.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>428 h</t>
+          <t>431 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -5186,9 +5186,9 @@
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>460.11</v>
-      </c>
-      <c r="O62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="16" t="n">
         <v>153.37</v>
       </c>
       <c r="P62" s="16" t="n">
@@ -5990,12 +5990,12 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
@@ -6030,29 +6030,29 @@
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>514.2</v>
-      </c>
-      <c r="O74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="16" t="n">
@@ -6062,32 +6062,32 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -6097,34 +6097,34 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33315</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00167138</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="13" t="n">
+        <v>149</v>
+      </c>
+      <c r="O75" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
@@ -6134,32 +6134,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6169,38 +6169,38 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>149</v>
-      </c>
-      <c r="O76" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O76" s="16" t="n">
+        <v>337.5</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0</v>
+        <v>385.71</v>
       </c>
     </row>
     <row r="77">
@@ -6257,53 +6257,53 @@
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>337.5</v>
+        <v>16</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>385.71</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6313,69 +6313,69 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>16</v>
+        <v>5733.25</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>18.29</v>
+        <v>2866.62</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6385,69 +6385,69 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="13" t="n">
-        <v>5733.25</v>
+        <v>400</v>
+      </c>
+      <c r="O79" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>2866.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
@@ -6469,52 +6469,52 @@
         <v>5</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>400</v>
-      </c>
-      <c r="O80" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>1400</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -6529,69 +6529,69 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="13" t="n">
-        <v>1400</v>
+        <v>400</v>
+      </c>
+      <c r="O81" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P81" s="13" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
@@ -6606,29 +6606,29 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>400</v>
-      </c>
-      <c r="O82" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="16" t="n">
@@ -6638,12 +6638,12 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -6678,29 +6678,29 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="13" t="n">
+        <v>940.506</v>
+      </c>
+      <c r="O83" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="13" t="n">
@@ -6710,12 +6710,12 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -6750,27 +6750,27 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>940.506</v>
+        <v>142.1</v>
       </c>
       <c r="O84" s="17" t="n">
         <v>0</v>
@@ -6782,27 +6782,27 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -6822,29 +6822,29 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O85" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="13" t="n">
@@ -6854,32 +6854,32 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -6889,49 +6889,49 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>0.25</v>
+        <v>3.5</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="16" t="n">
-        <v>0</v>
+        <v>1122</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0</v>
+        <v>320.57</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6966,64 +6966,64 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="13" t="n">
-        <v>1122</v>
+        <v>450</v>
+      </c>
+      <c r="O87" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>320.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G88" s="15" t="inlineStr">
@@ -7033,69 +7033,69 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O88" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O88" s="16" t="n">
+        <v>136.5</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -7105,64 +7105,64 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="13" t="n">
-        <v>136.5</v>
+        <v>3240</v>
+      </c>
+      <c r="O89" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P89" s="13" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
@@ -7193,16 +7193,16 @@
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>3240</v>
+        <v>1000</v>
       </c>
       <c r="O90" s="17" t="n">
         <v>0</v>
@@ -7214,27 +7214,27 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
@@ -7265,19 +7265,19 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O91" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>203.5</v>
       </c>
       <c r="P91" s="13" t="n">
         <v>0</v>
@@ -7286,12 +7286,12 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
@@ -7337,19 +7337,19 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="16" t="n">
-        <v>203.5</v>
+        <v>823.65</v>
       </c>
       <c r="P92" s="16" t="n">
         <v>0</v>
@@ -7358,32 +7358,32 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -7393,35 +7393,35 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="13" t="n">
-        <v>823.65</v>
+        <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
         <v>0</v>
@@ -7430,32 +7430,32 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
@@ -7465,34 +7465,34 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="16" t="n">
+        <v>285</v>
+      </c>
+      <c r="O94" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
@@ -7502,32 +7502,32 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -7542,29 +7542,29 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>285</v>
-      </c>
-      <c r="O95" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
@@ -7574,12 +7574,12 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -7614,29 +7614,29 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="O96" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7646,32 +7646,32 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
@@ -7697,19 +7697,19 @@
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>120</v>
-      </c>
-      <c r="O97" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O97" s="13" t="n">
+        <v>73.5</v>
       </c>
       <c r="P97" s="13" t="n">
         <v>0</v>
@@ -7718,12 +7718,12 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7758,64 +7758,64 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>73.5</v>
+        <v>1470</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31735</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[EVREUX] - Initiation à la redevance</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE EVREUX</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Initiation à la redevance</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -7825,69 +7825,69 @@
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31739</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00158914</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="O99" s="13" t="n">
-        <v>1470</v>
+        <v>0</v>
       </c>
       <c r="P99" s="13" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31735</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[EVREUX] - Initiation à la redevance</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE EVREUX</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Initiation à la redevance</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G100" s="15" t="inlineStr">
@@ -7897,34 +7897,34 @@
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31739</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00158914</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="16" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O100" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
@@ -7934,12 +7934,12 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
@@ -7985,16 +7985,16 @@
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>203.5</v>
+        <v>1500</v>
       </c>
       <c r="O101" s="17" t="n">
         <v>0</v>
@@ -8006,69 +8006,61 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G102" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31596</t>
-        </is>
-      </c>
-      <c r="M102" s="15" t="inlineStr">
-        <is>
-          <t>00157967</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L102" s="15" t="inlineStr"/>
+      <c r="M102" s="15" t="inlineStr"/>
       <c r="N102" s="16" t="n">
-        <v>1500</v>
-      </c>
-      <c r="O102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8078,96 +8070,104 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L103" s="12" t="inlineStr"/>
-      <c r="M103" s="12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L103" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31488</t>
+        </is>
+      </c>
+      <c r="M103" s="12" t="inlineStr">
+        <is>
+          <t>00157472</t>
+        </is>
+      </c>
       <c r="N103" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O103" s="13" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="P103" s="13" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
@@ -8177,69 +8177,69 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="16" t="n">
-        <v>130</v>
+        <v>27.765</v>
+      </c>
+      <c r="O104" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -8249,32 +8249,32 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>27.765</v>
+        <v>210</v>
       </c>
       <c r="O105" s="17" t="n">
         <v>0</v>
@@ -8286,12 +8286,12 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
@@ -8337,19 +8337,19 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>210</v>
-      </c>
-      <c r="O106" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O106" s="16" t="n">
+        <v>281</v>
       </c>
       <c r="P106" s="16" t="n">
         <v>0</v>
@@ -8358,32 +8358,32 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G107" s="12" t="inlineStr">
@@ -8393,35 +8393,35 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O107" s="13" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="P107" s="13" t="n">
         <v>0</v>
@@ -8430,32 +8430,32 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G108" s="15" t="inlineStr">
@@ -8465,34 +8465,34 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="O108" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8502,12 +8502,12 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
@@ -8553,16 +8553,16 @@
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O109" s="17" t="n">
         <v>0</v>
@@ -8574,12 +8574,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E110" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
@@ -8614,27 +8614,27 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K110" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="O110" s="17" t="n">
         <v>0</v>
@@ -8646,32 +8646,32 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -8681,34 +8681,34 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
-        <v>140</v>
-      </c>
-      <c r="O111" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
@@ -8718,27 +8718,27 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
@@ -8758,23 +8758,23 @@
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8790,32 +8790,32 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29685</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Migration V2 ODP</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -8825,34 +8825,34 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29690</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152489</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="13" t="n">
+        <v>532.37</v>
+      </c>
+      <c r="O113" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="13" t="n">
@@ -8862,32 +8862,32 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29685</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E114" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 ODP</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G114" s="15" t="inlineStr">
@@ -8897,38 +8897,38 @@
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29690</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00152489</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>532.37</v>
-      </c>
-      <c r="O114" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O114" s="16" t="n">
+        <v>448.1</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0</v>
+        <v>488.84</v>
       </c>
     </row>
     <row r="115">
@@ -8985,22 +8985,22 @@
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="13" t="n">
-        <v>448.1</v>
+        <v>125</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>488.84</v>
+        <v>136.36</v>
       </c>
     </row>
     <row r="116">
@@ -9057,49 +9057,47 @@
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O116" s="16" t="n">
-        <v>125</v>
+        <v>525</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>136.36</v>
+        <v>572.73</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>Paramétrages complémentaires + Vision</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v/>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
@@ -9118,54 +9116,54 @@
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>0.92</v>
+        <v>0.25</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O117" s="13" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="P117" s="13" t="n">
-        <v>572.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28653</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>PALAVAS LES FLOTS - GEODP2 migration</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
+          <t>PALAVAS LES FLOTS</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9173,7 +9171,7 @@
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G118" s="15" t="inlineStr">
@@ -9183,34 +9181,34 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28657</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00146509</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" s="16" t="n">
+        <v>1946.67</v>
+      </c>
+      <c r="O118" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="16" t="n">
@@ -9220,26 +9218,28 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28653</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>PALAVAS LES FLOTS - GEODP2 migration</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>PALAVAS LES FLOTS</t>
-        </is>
-      </c>
-      <c r="E119" s="12" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
@@ -9258,30 +9258,30 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28657</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00146509</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>1946.67</v>
-      </c>
-      <c r="O119" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O119" s="13" t="n">
+        <v>362.5</v>
       </c>
       <c r="P119" s="13" t="n">
         <v>0</v>
@@ -9290,27 +9290,27 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-28237</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>VILLE DE VANNES - SEPA pour activité marché</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E120" s="15" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>SEPA pour activité marché</t>
         </is>
       </c>
       <c r="F120" s="15" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
@@ -9341,19 +9341,19 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28238</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145118</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="16" t="n">
-        <v>362.5</v>
+        <v>810</v>
+      </c>
+      <c r="O120" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
         <v>0</v>
@@ -9362,32 +9362,30 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28237</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES - SEPA pour activité marché</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="inlineStr">
-        <is>
-          <t>SEPA pour activité marché</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v/>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -9397,34 +9395,34 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28238</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>00145118</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
-        <v>810</v>
-      </c>
-      <c r="O121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="13" t="n">
@@ -9434,12 +9432,12 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
@@ -9449,11 +9447,13 @@
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
@@ -9472,23 +9472,23 @@
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>6.5</v>
+        <v>2.45</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9699,12 +9699,12 @@
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9792,12 +9792,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Adaptation Modèle et FDS</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9807,13 +9807,11 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="n">
+        <v/>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
@@ -9827,34 +9825,34 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="13" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="O127" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9864,12 +9862,12 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Adaptation Modèle et FDS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
@@ -9879,52 +9877,38 @@
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v/>
-      </c>
-      <c r="F128" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F128" s="15" t="inlineStr"/>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H128" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="inlineStr"/>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27642</t>
-        </is>
-      </c>
-      <c r="M128" s="15" t="inlineStr">
-        <is>
-          <t>00143935</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr"/>
+      <c r="M128" s="15" t="inlineStr"/>
       <c r="N128" s="16" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="O128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9934,12 +9918,12 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -9949,34 +9933,48 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F129" s="12" t="inlineStr"/>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" s="12" t="inlineStr"/>
-      <c r="M129" s="12" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-26814</t>
+        </is>
+      </c>
+      <c r="M129" s="12" t="inlineStr">
+        <is>
+          <t>00142941</t>
+        </is>
+      </c>
       <c r="N129" s="13" t="n">
         <v>0</v>
       </c>
@@ -9990,22 +9988,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-24880</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[CD 76] - Modélisation complémentaire 28H</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>DEPARTEMENT DE LA SEINE MARITIME (CD 76)</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -10028,23 +10026,23 @@
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27048</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>0014120</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
@@ -10060,12 +10058,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24880</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[CD 76] - Modélisation complémentaire 28H</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -10075,11 +10073,13 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA SEINE MARITIME (CD 76)</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
@@ -10093,28 +10093,28 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27048</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>0014120</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
@@ -10130,12 +10130,12 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
@@ -10145,13 +10145,11 @@
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E132" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+        </is>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v/>
       </c>
       <c r="F132" s="15" t="inlineStr">
         <is>
@@ -10165,28 +10163,28 @@
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N132" s="16" t="n">
@@ -10202,12 +10200,12 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -10217,7 +10215,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10240,23 +10238,23 @@
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10272,12 +10270,12 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
@@ -10287,7 +10285,7 @@
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10305,28 +10303,28 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10391,12 +10389,12 @@
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10412,22 +10410,22 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10450,44 +10448,44 @@
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O136" s="16" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P136" s="16" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10497,11 +10495,13 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E137" s="12" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
@@ -10510,54 +10510,54 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
         <v>13</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O137" s="13" t="n">
-        <v>416.188</v>
+        <v>0</v>
       </c>
       <c r="P137" s="13" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
@@ -10567,13 +10567,11 @@
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E138" s="15" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>VILLE DE BAGNOLET</t>
+        </is>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v/>
       </c>
       <c r="F138" s="15" t="inlineStr">
         <is>
@@ -10582,33 +10580,33 @@
       </c>
       <c r="G138" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
@@ -10624,12 +10622,12 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
@@ -10639,7 +10637,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10662,23 +10660,23 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>1.75</v>
+        <v>0.12</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
@@ -10739,16 +10737,16 @@
         <v>14</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
@@ -10779,7 +10777,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10809,16 +10807,16 @@
         <v>14</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
@@ -10849,7 +10847,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10879,16 +10877,16 @@
         <v>14</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
@@ -10904,12 +10902,12 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22494</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[VILLEJUIF] - LITTERALIS FLUX WFS sortant</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
@@ -10919,7 +10917,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10932,35 +10930,27 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L143" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27365</t>
-        </is>
-      </c>
-      <c r="M143" s="12" t="inlineStr">
-        <is>
-          <t>491593</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L143" s="12" t="inlineStr"/>
+      <c r="M143" s="12" t="inlineStr"/>
       <c r="N143" s="13" t="n">
         <v>0</v>
       </c>
@@ -10974,12 +10964,12 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22494</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS FLUX WFS sortant</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
@@ -10989,7 +10979,7 @@
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -11002,7 +10992,7 @@
       </c>
       <c r="G144" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H144" s="15" t="inlineStr">
@@ -11012,7 +11002,7 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
@@ -11021,8 +11011,16 @@
       <c r="K144" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="L144" s="15" t="inlineStr"/>
-      <c r="M144" s="15" t="inlineStr"/>
+      <c r="L144" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27368</t>
+        </is>
+      </c>
+      <c r="M144" s="15" t="inlineStr">
+        <is>
+          <t>484163</t>
+        </is>
+      </c>
       <c r="N144" s="16" t="n">
         <v>0</v>
       </c>
@@ -11036,22 +11034,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-21548</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>[Evreux] AME</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>EVREUX</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11074,23 +11072,23 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-28039</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>477841</t>
         </is>
       </c>
       <c r="N145" s="13" t="n">
@@ -11106,12 +11104,12 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21548</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[Evreux] AME</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
@@ -11121,7 +11119,7 @@
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>EVREUX</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11139,28 +11137,28 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>0.75</v>
+        <v>10.5</v>
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28039</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>477841</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N146" s="16" t="n">
@@ -11176,22 +11174,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11209,28 +11207,28 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>10.5</v>
+        <v>1</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
@@ -11246,22 +11244,22 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11284,29 +11282,29 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N148" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O148" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O148" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P148" s="16" t="n">
@@ -11316,12 +11314,12 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -11331,7 +11329,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11349,34 +11347,34 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N149" s="13" t="n">
-        <v>230</v>
-      </c>
-      <c r="O149" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P149" s="13" t="n">
@@ -11386,12 +11384,12 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
@@ -11401,7 +11399,7 @@
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11419,34 +11417,34 @@
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
         <v>18</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M150" s="15" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N150" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="O150" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P150" s="16" t="n">
@@ -11456,22 +11454,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11489,34 +11487,34 @@
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N151" s="13" t="n">
-        <v>350</v>
-      </c>
-      <c r="O151" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P151" s="13" t="n">
@@ -11575,12 +11573,12 @@
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28214</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>458286</t>
         </is>
       </c>
       <c r="N152" s="16" t="n">
@@ -11596,22 +11594,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11634,23 +11632,23 @@
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N153" s="13" t="n">
@@ -11666,22 +11664,22 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19093</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[FREJUS] Accompagnement</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11689,7 +11687,7 @@
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G154" s="15" t="inlineStr">
@@ -11699,34 +11697,34 @@
       </c>
       <c r="H154" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>13/02/2025</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-28024</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>465057</t>
         </is>
       </c>
       <c r="N154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" s="16" t="n">
+        <v>515</v>
+      </c>
+      <c r="O154" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P154" s="16" t="n">
@@ -11736,22 +11734,22 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19093</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[FREJUS] Accompagnement</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11759,12 +11757,12 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
@@ -11774,29 +11772,21 @@
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>13/02/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28024</t>
-        </is>
-      </c>
-      <c r="M155" s="12" t="inlineStr">
-        <is>
-          <t>465057</t>
-        </is>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="L155" s="12" t="inlineStr"/>
+      <c r="M155" s="12" t="inlineStr"/>
       <c r="N155" s="13" t="n">
-        <v>515</v>
-      </c>
-      <c r="O155" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P155" s="13" t="n">
@@ -11806,22 +11796,22 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11839,7 +11829,7 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
@@ -11851,7 +11841,7 @@
         <v>21</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>6.5</v>
+        <v>25.58</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -11868,12 +11858,12 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
@@ -11883,7 +11873,7 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11906,14 +11896,14 @@
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
         <v>21</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>25.58</v>
+        <v>0.25</v>
       </c>
       <c r="L157" s="12" t="inlineStr"/>
       <c r="M157" s="12" t="inlineStr"/>
@@ -11930,22 +11920,22 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11953,36 +11943,44 @@
       </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G158" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>21</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L158" s="15" t="inlineStr"/>
-      <c r="M158" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L158" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M158" s="15" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N158" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O158" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P158" s="16" t="n">
@@ -11992,22 +11990,22 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -12015,7 +12013,7 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
@@ -12025,34 +12023,34 @@
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
         <v>21</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N159" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O159" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P159" s="13" t="n">
@@ -12077,7 +12075,7 @@
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12111,7 +12109,7 @@
       </c>
       <c r="L160" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M160" s="15" t="inlineStr">
@@ -12132,22 +12130,22 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-17710</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Saint Lo] Migration</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>Saint Lo</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -12155,40 +12153,28 @@
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G161" s="12" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G161" s="12" t="inlineStr"/>
       <c r="H161" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>25/11/2024</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L161" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28020</t>
-        </is>
-      </c>
-      <c r="M161" s="12" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L161" s="12" t="inlineStr"/>
+      <c r="M161" s="12" t="inlineStr"/>
       <c r="N161" s="13" t="n">
         <v>0</v>
       </c>
@@ -12202,22 +12188,22 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-17710</t>
+          <t>PDMDEP-16116</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[Saint Lo] Migration</t>
+          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>Saint Lo</t>
+          <t>CD 01</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12225,25 +12211,29 @@
       </c>
       <c r="F162" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G162" s="15" t="inlineStr"/>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G162" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>25/11/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L162" s="15" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -12260,22 +12250,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16116</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>CD 01</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12298,11 +12288,11 @@
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J163" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K163" s="12" t="n">
         <v>0.5</v>
@@ -12322,22 +12312,22 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12360,14 +12350,14 @@
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L164" s="15" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -13458,13 +13448,13 @@
       <c r="L183" s="18" t="inlineStr"/>
       <c r="M183" s="18" t="inlineStr"/>
       <c r="N183" s="19" t="n">
-        <v>48185.576</v>
+        <v>47211.266</v>
       </c>
       <c r="O183" s="19" t="n">
-        <v>51747.578</v>
+        <v>51747.57799999999</v>
       </c>
       <c r="P183" s="19" t="n">
-        <v>180.88</v>
+        <v>180.42</v>
       </c>
     </row>
   </sheetData>
@@ -14891,26 +14881,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>146.92</v>
+        <v>147.42</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>48.67</v>
+        <v>48.92</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>19.25</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>214.83</v>
+        <v>215.58</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>29.17</v>
+        <v>30.17</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>427.88</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14942,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>102</v>
+        <v>103.25</v>
       </c>
     </row>
   </sheetData>
@@ -15037,10 +15027,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>400848</v>
+        <v>415523</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>173465</v>
+        <v>188140</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>227383</v>
@@ -15087,10 +15077,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>223139</v>
+        <v>237814</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>121619</v>
+        <v>136294</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>101520</v>
@@ -15116,7 +15106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15140,7 +15130,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 26 commande(s)</t>
+          <t>Épics créées ce mois — 27 commande(s)</t>
         </is>
       </c>
     </row>
@@ -15195,22 +15185,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35912</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35905</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -15230,32 +15220,32 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00182377</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>0</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35636</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35627</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE D'ANNEMASSE</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -15275,32 +15265,32 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00181182</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
-        <v>6285</v>
+        <v>9264</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -15313,35 +15303,39 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr"/>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00180831</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>1450</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35587</t>
+          <t>PDMDEP-35672</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35583</t>
+          <t>PDMDEP-35666</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -15351,7 +15345,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -15361,32 +15355,32 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00180931</t>
+          <t>00181382</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35606</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35597</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -15399,39 +15393,35 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G9" s="15" t="inlineStr"/>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00181049</t>
+          <t>00180831</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>0</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35636</t>
+          <t>PDMDEP-35733</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35627</t>
+          <t>PDMDEP-35727</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANNEMASSE</t>
+          <t>COMMUNE DE VIEUX BOUCAU</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -15451,32 +15441,32 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00181182</t>
+          <t>00181531</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>9264</v>
+        <v>4815</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35747</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35743</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE D'EYSINES</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -15486,7 +15476,7 @@
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -15496,32 +15486,32 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00181626</t>
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35672</t>
+          <t>PDMDEP-35606</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35666</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -15541,32 +15531,32 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>00181382</t>
+          <t>00181049</t>
         </is>
       </c>
       <c r="I12" s="27" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35733</t>
+          <t>PDMDEP-35758</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35727</t>
+          <t>PDMDEP-35752</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIEUX BOUCAU</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -15576,7 +15566,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -15586,32 +15576,32 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>00181531</t>
+          <t>00181622</t>
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>4815</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -15631,32 +15621,32 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I14" s="27" t="n">
-        <v>28915.01</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35758</t>
+          <t>PDMDEP-35857</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35752</t>
+          <t>PDMDEP-35853</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>MAIRIE DE BOURG SAINT ANDEOL</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -15676,22 +15666,22 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>00181622</t>
+          <t>00182113</t>
         </is>
       </c>
       <c r="I15" s="26" t="n">
-        <v>4900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35857</t>
+          <t>PDMDEP-35872</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35853</t>
+          <t>PDMDEP-35863</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -15701,7 +15691,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE BOURG SAINT ANDEOL</t>
+          <t>COMMUNE DE DIJON</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -15711,7 +15701,7 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -15721,32 +15711,32 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>00182113</t>
+          <t>00182115</t>
         </is>
       </c>
       <c r="I16" s="27" t="n">
-        <v>0</v>
+        <v>12590</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35872</t>
+          <t>PDMDEP-35912</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35863</t>
+          <t>PDMDEP-35905</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE DIJON</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -15766,32 +15756,32 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>00182115</t>
+          <t>00182377</t>
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>0</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35747</t>
+          <t>PDMDEP-35587</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35743</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -15811,7 +15801,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>00181626</t>
+          <t>00180931</t>
         </is>
       </c>
       <c r="I18" s="27" t="n">
@@ -15821,22 +15811,22 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35687</t>
+          <t>PDMDEP-35464</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35683</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -15856,32 +15846,32 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>00181396</t>
+          <t>00180631</t>
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>2333.33</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35771</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35767</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -15901,32 +15891,32 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>00181751</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>2740</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35788</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35782</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -15946,32 +15936,32 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>00181845</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
-        <v>1412.5</v>
+        <v>895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -15981,7 +15971,7 @@
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -15991,7 +15981,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
@@ -16001,22 +15991,22 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35945</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35941</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>Commune de Dunkerque</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -16036,32 +16026,32 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00182674</t>
         </is>
       </c>
       <c r="I23" s="26" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -16081,32 +16071,32 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35889</t>
+          <t>PDMDEP-35687</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35883</t>
+          <t>PDMDEP-35683</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -16126,32 +16116,32 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>00182197</t>
+          <t>00181396</t>
         </is>
       </c>
       <c r="I25" s="26" t="n">
-        <v>5895</v>
+        <v>2333.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35771</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35767</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -16161,7 +16151,7 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -16171,32 +16161,32 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00181751</t>
         </is>
       </c>
       <c r="I26" s="27" t="n">
-        <v>0</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35902</t>
+          <t>PDMDEP-35788</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35840</t>
+          <t>PDMDEP-35782</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -16209,35 +16199,39 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G27" s="15" t="inlineStr"/>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>00182109</t>
+          <t>00181845</t>
         </is>
       </c>
       <c r="I27" s="26" t="n">
-        <v>895</v>
+        <v>1412.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35889</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35883</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -16257,32 +16251,32 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00182197</t>
         </is>
       </c>
       <c r="I28" s="27" t="n">
-        <v>455</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35439</t>
+          <t>PDMDEP-35902</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35840</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -16295,90 +16289,110 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G29" s="15" t="inlineStr"/>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>00180506</t>
+          <t>00182109</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>3974</v>
+        <v>895</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
+          <t>PDMDEP-35576</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-35572</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>00180891</t>
+        </is>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-35652</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-35646</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>VILLE DE GEX</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G31" s="15" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="H31" s="15" t="inlineStr">
         <is>
           <t>00181167</t>
         </is>
       </c>
-      <c r="I30" s="27" t="n">
+      <c r="I31" s="26" t="n">
         <v>6382.5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t>26 commande(s)</t>
-        </is>
-      </c>
-      <c r="I31" s="25" t="n">
-        <v>83126</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B32" s="18" t="n"/>
@@ -16389,17 +16403,17 @@
       <c r="G32" s="18" t="n"/>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>12 commande(s)</t>
+          <t>27 commande(s)</t>
         </is>
       </c>
       <c r="I32" s="25" t="n">
-        <v>25822</v>
+        <v>97451</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B33" s="18" t="n"/>
@@ -16410,11 +16424,32 @@
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="18" t="inlineStr">
         <is>
+          <t>13 commande(s)</t>
+        </is>
+      </c>
+      <c r="I33" s="25" t="n">
+        <v>25822</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="18" t="inlineStr">
+        <is>
           <t>14 commande(s)</t>
         </is>
       </c>
-      <c r="I33" s="25" t="n">
-        <v>57304</v>
+      <c r="I34" s="25" t="n">
+        <v>71629</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-28.xlsx
+++ b/jira_export_2026-09-28.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>431 h</t>
+          <t>450 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P183"/>
+  <dimension ref="A1:P182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>89.5</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>23.87</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="13">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="N23" s="13" t="n">
-        <v>0</v>
+        <v>225.45</v>
       </c>
       <c r="O23" s="13" t="n">
         <v>250.5</v>
@@ -4457,7 +4457,7 @@
         <v>3</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>72</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>72</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="53">
@@ -4885,7 +4885,7 @@
         <v>3</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>51</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>34</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="59">
@@ -5389,7 +5389,7 @@
         <v>3</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
@@ -7070,27 +7070,27 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
@@ -7121,16 +7121,16 @@
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>3240</v>
+        <v>1000</v>
       </c>
       <c r="O89" s="17" t="n">
         <v>0</v>
@@ -7142,27 +7142,27 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
@@ -7193,19 +7193,19 @@
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O90" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O90" s="16" t="n">
+        <v>203.5</v>
       </c>
       <c r="P90" s="16" t="n">
         <v>0</v>
@@ -7214,12 +7214,12 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
@@ -7265,19 +7265,19 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>203.5</v>
+        <v>823.65</v>
       </c>
       <c r="P91" s="13" t="n">
         <v>0</v>
@@ -7286,32 +7286,32 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -7321,35 +7321,35 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="16" t="n">
-        <v>823.65</v>
+        <v>0</v>
       </c>
       <c r="P92" s="16" t="n">
         <v>0</v>
@@ -7358,32 +7358,32 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -7393,34 +7393,34 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="13" t="n">
+        <v>285</v>
+      </c>
+      <c r="O93" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
@@ -7430,32 +7430,32 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
@@ -7470,29 +7470,29 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>285</v>
-      </c>
-      <c r="O94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
@@ -7502,12 +7502,12 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7542,29 +7542,29 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="O95" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
@@ -7574,32 +7574,32 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
@@ -7625,19 +7625,19 @@
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="O96" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>73.5</v>
       </c>
       <c r="P96" s="16" t="n">
         <v>0</v>
@@ -7646,12 +7646,12 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -7686,64 +7686,64 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="O97" s="13" t="n">
-        <v>73.5</v>
+        <v>1470</v>
       </c>
       <c r="P97" s="13" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31735</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[EVREUX] - Initiation à la redevance</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE EVREUX</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Initiation à la redevance</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G98" s="15" t="inlineStr">
@@ -7753,69 +7753,69 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31739</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00158914</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>1470</v>
+        <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31735</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[EVREUX] - Initiation à la redevance</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE EVREUX</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Initiation à la redevance</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -7825,34 +7825,34 @@
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31739</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00158914</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="13" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O99" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="13" t="n">
@@ -7862,12 +7862,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
@@ -7913,16 +7913,16 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>203.5</v>
+        <v>1500</v>
       </c>
       <c r="O100" s="17" t="n">
         <v>0</v>
@@ -7934,69 +7934,61 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-31596</t>
-        </is>
-      </c>
-      <c r="M101" s="12" t="inlineStr">
-        <is>
-          <t>00157967</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L101" s="12" t="inlineStr"/>
+      <c r="M101" s="12" t="inlineStr"/>
       <c r="N101" s="13" t="n">
-        <v>1500</v>
-      </c>
-      <c r="O101" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="13" t="n">
@@ -8006,96 +7998,104 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G102" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L102" s="15" t="inlineStr"/>
-      <c r="M102" s="15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L102" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31488</t>
+        </is>
+      </c>
+      <c r="M102" s="15" t="inlineStr">
+        <is>
+          <t>00157472</t>
+        </is>
+      </c>
       <c r="N102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O102" s="16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -8105,69 +8105,69 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="13" t="n">
-        <v>130</v>
+        <v>27.765</v>
+      </c>
+      <c r="O103" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
@@ -8177,32 +8177,32 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>27.765</v>
+        <v>210</v>
       </c>
       <c r="O104" s="17" t="n">
         <v>0</v>
@@ -8214,12 +8214,12 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -8265,19 +8265,19 @@
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>210</v>
-      </c>
-      <c r="O105" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O105" s="13" t="n">
+        <v>281</v>
       </c>
       <c r="P105" s="13" t="n">
         <v>0</v>
@@ -8286,32 +8286,32 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G106" s="15" t="inlineStr">
@@ -8321,35 +8321,35 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O106" s="16" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="P106" s="16" t="n">
         <v>0</v>
@@ -8358,32 +8358,32 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G107" s="12" t="inlineStr">
@@ -8393,34 +8393,34 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="O107" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="13" t="n">
@@ -8430,12 +8430,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
@@ -8481,16 +8481,16 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O108" s="17" t="n">
         <v>0</v>
@@ -8502,12 +8502,12 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
@@ -8542,27 +8542,27 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="O109" s="17" t="n">
         <v>0</v>
@@ -8574,32 +8574,32 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E110" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G110" s="15" t="inlineStr">
@@ -8609,34 +8609,34 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="O110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8646,27 +8646,27 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -8686,23 +8686,23 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
@@ -8718,32 +8718,32 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29685</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Migration V2 ODP</t>
         </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G112" s="15" t="inlineStr">
@@ -8753,34 +8753,34 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29690</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152489</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="16" t="n">
+        <v>532.37</v>
+      </c>
+      <c r="O112" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="16" t="n">
@@ -8790,32 +8790,32 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29685</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 ODP</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -8825,38 +8825,38 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29690</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00152489</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>532.37</v>
-      </c>
-      <c r="O113" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O113" s="13" t="n">
+        <v>448.1</v>
       </c>
       <c r="P113" s="13" t="n">
-        <v>0</v>
+        <v>488.84</v>
       </c>
     </row>
     <row r="114">
@@ -8913,22 +8913,22 @@
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O114" s="16" t="n">
-        <v>448.1</v>
+        <v>125</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>488.84</v>
+        <v>136.36</v>
       </c>
     </row>
     <row r="115">
@@ -8985,49 +8985,47 @@
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="13" t="n">
-        <v>125</v>
+        <v>525</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>136.36</v>
+        <v>572.73</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
-        <is>
-          <t>Paramétrages complémentaires + Vision</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v/>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
@@ -9046,54 +9044,54 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O116" s="16" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>572.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28653</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>PALAVAS LES FLOTS - GEODP2 migration</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
+          <t>PALAVAS LES FLOTS</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
@@ -9101,7 +9099,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -9111,34 +9109,34 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28657</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00146509</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="13" t="n">
+        <v>1946.67</v>
+      </c>
+      <c r="O117" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="13" t="n">
@@ -9148,26 +9146,28 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28653</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>PALAVAS LES FLOTS - GEODP2 migration</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>PALAVAS LES FLOTS</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -9186,30 +9186,30 @@
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K118" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28657</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00146509</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
-        <v>1946.67</v>
-      </c>
-      <c r="O118" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O118" s="16" t="n">
+        <v>362.5</v>
       </c>
       <c r="P118" s="16" t="n">
         <v>0</v>
@@ -9218,27 +9218,27 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-28237</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>VILLE DE VANNES - SEPA pour activité marché</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>SEPA pour activité marché</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
@@ -9253,12 +9253,12 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
@@ -9269,19 +9269,19 @@
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28238</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145118</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" s="13" t="n">
-        <v>362.5</v>
+        <v>810</v>
+      </c>
+      <c r="O119" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P119" s="13" t="n">
         <v>0</v>
@@ -9290,32 +9290,30 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28237</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES - SEPA pour activité marché</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
-        </is>
-      </c>
-      <c r="E120" s="15" t="inlineStr">
-        <is>
-          <t>SEPA pour activité marché</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v/>
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G120" s="15" t="inlineStr">
@@ -9325,34 +9323,34 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28238</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00145118</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>810</v>
-      </c>
-      <c r="O120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9362,12 +9360,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9377,11 +9375,13 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
@@ -9400,23 +9400,23 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>6.5</v>
+        <v>2.55</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9479,16 +9479,16 @@
         <v>10</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9551,16 +9551,16 @@
         <v>10</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9623,16 +9623,16 @@
         <v>10</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9695,16 +9695,16 @@
         <v>10</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9720,12 +9720,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Adaptation Modèle et FDS</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9735,13 +9735,11 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E126" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v/>
       </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
@@ -9755,34 +9753,34 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="16" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="O126" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="16" t="n">
@@ -9792,12 +9790,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Adaptation Modèle et FDS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9807,52 +9805,38 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="n">
-        <v/>
-      </c>
-      <c r="F127" s="12" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr"/>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr"/>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L127" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27642</t>
-        </is>
-      </c>
-      <c r="M127" s="12" t="inlineStr">
-        <is>
-          <t>00143935</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L127" s="12" t="inlineStr"/>
+      <c r="M127" s="12" t="inlineStr"/>
       <c r="N127" s="13" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="O127" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9862,12 +9846,12 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
@@ -9877,34 +9861,48 @@
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F128" s="15" t="inlineStr"/>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F128" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H128" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr"/>
-      <c r="M128" s="15" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-26814</t>
+        </is>
+      </c>
+      <c r="M128" s="15" t="inlineStr">
+        <is>
+          <t>00142941</t>
+        </is>
+      </c>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
@@ -9918,22 +9916,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-24880</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[CD 76] - Modélisation complémentaire 28H</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>DEPARTEMENT DE LA SEINE MARITIME (CD 76)</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9956,23 +9954,23 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27048</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>0014120</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
@@ -9988,12 +9986,12 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24880</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[CD 76] - Modélisation complémentaire 28H</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
@@ -10003,11 +10001,13 @@
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA SEINE MARITIME (CD 76)</t>
-        </is>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
@@ -10021,28 +10021,28 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27048</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>0014120</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
@@ -10058,12 +10058,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -10073,13 +10073,11 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="n">
+        <v/>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
@@ -10093,28 +10091,28 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
@@ -10130,12 +10128,12 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
@@ -10145,7 +10143,7 @@
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10168,23 +10166,23 @@
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N132" s="16" t="n">
@@ -10200,12 +10198,12 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -10215,7 +10213,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10233,28 +10231,28 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10319,12 +10317,12 @@
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10340,22 +10338,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10378,44 +10376,44 @@
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O135" s="13" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P135" s="13" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
@@ -10425,11 +10423,13 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E136" s="15" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E136" s="15" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
@@ -10438,54 +10438,54 @@
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O136" s="16" t="n">
-        <v>416.188</v>
+        <v>0</v>
       </c>
       <c r="P136" s="16" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10495,13 +10495,11 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E137" s="12" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>VILLE DE BAGNOLET</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="n">
+        <v/>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
@@ -10510,33 +10508,33 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
@@ -10552,12 +10550,12 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
@@ -10567,7 +10565,7 @@
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10590,23 +10588,23 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
         <v>14</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>1.75</v>
+        <v>0.12</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
@@ -10671,12 +10669,12 @@
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
@@ -10707,7 +10705,7 @@
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10741,12 +10739,12 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
@@ -10777,7 +10775,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10811,12 +10809,12 @@
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
@@ -10832,12 +10830,12 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22494</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[VILLEJUIF] - LITTERALIS FLUX WFS sortant</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
@@ -10847,7 +10845,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10860,35 +10858,27 @@
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L142" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27365</t>
-        </is>
-      </c>
-      <c r="M142" s="15" t="inlineStr">
-        <is>
-          <t>491593</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L142" s="15" t="inlineStr"/>
+      <c r="M142" s="15" t="inlineStr"/>
       <c r="N142" s="16" t="n">
         <v>0</v>
       </c>
@@ -10902,12 +10892,12 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22494</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS FLUX WFS sortant</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
@@ -10917,7 +10907,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10930,7 +10920,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -10940,7 +10930,7 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
@@ -10949,8 +10939,16 @@
       <c r="K143" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="L143" s="12" t="inlineStr"/>
-      <c r="M143" s="12" t="inlineStr"/>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27368</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>484163</t>
+        </is>
+      </c>
       <c r="N143" s="13" t="n">
         <v>0</v>
       </c>
@@ -10964,22 +10962,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-21548</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>[Evreux] AME</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>EVREUX</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -11002,23 +11000,23 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-28039</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>477841</t>
         </is>
       </c>
       <c r="N144" s="16" t="n">
@@ -11034,12 +11032,12 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21548</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[Evreux] AME</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
@@ -11049,7 +11047,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>EVREUX</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11067,28 +11065,28 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>0.75</v>
+        <v>10.5</v>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28039</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>477841</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N145" s="13" t="n">
@@ -11104,22 +11102,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11137,28 +11135,28 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>10.5</v>
+        <v>1</v>
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N146" s="16" t="n">
@@ -11174,22 +11172,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11212,29 +11210,29 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" s="13" t="n">
+        <v>230</v>
+      </c>
+      <c r="O147" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P147" s="13" t="n">
@@ -11244,12 +11242,12 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -11259,7 +11257,7 @@
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11277,34 +11275,34 @@
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N148" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O148" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P148" s="16" t="n">
@@ -11314,12 +11312,12 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -11329,7 +11327,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11347,34 +11345,34 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N149" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="O149" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P149" s="13" t="n">
@@ -11384,22 +11382,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11417,34 +11415,34 @@
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M150" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N150" s="16" t="n">
-        <v>350</v>
-      </c>
-      <c r="O150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P150" s="16" t="n">
@@ -11503,12 +11501,12 @@
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28214</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>458286</t>
         </is>
       </c>
       <c r="N151" s="13" t="n">
@@ -11524,22 +11522,22 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11562,23 +11560,23 @@
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N152" s="16" t="n">
@@ -11594,22 +11592,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19093</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[FREJUS] Accompagnement</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11617,7 +11615,7 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -11627,34 +11625,34 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>13/02/2025</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-28024</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>465057</t>
         </is>
       </c>
       <c r="N153" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" s="13" t="n">
+        <v>515</v>
+      </c>
+      <c r="O153" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P153" s="13" t="n">
@@ -11664,22 +11662,22 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19093</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[FREJUS] Accompagnement</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11687,12 +11685,12 @@
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G154" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H154" s="15" t="inlineStr">
@@ -11702,29 +11700,21 @@
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>13/02/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28024</t>
-        </is>
-      </c>
-      <c r="M154" s="15" t="inlineStr">
-        <is>
-          <t>465057</t>
-        </is>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="L154" s="15" t="inlineStr"/>
+      <c r="M154" s="15" t="inlineStr"/>
       <c r="N154" s="16" t="n">
-        <v>515</v>
-      </c>
-      <c r="O154" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P154" s="16" t="n">
@@ -11734,22 +11724,22 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11767,7 +11757,7 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
@@ -11779,7 +11769,7 @@
         <v>21</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>6.5</v>
+        <v>25.58</v>
       </c>
       <c r="L155" s="12" t="inlineStr"/>
       <c r="M155" s="12" t="inlineStr"/>
@@ -11796,12 +11786,12 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
@@ -11811,7 +11801,7 @@
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11834,14 +11824,14 @@
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
         <v>21</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>25.58</v>
+        <v>0.25</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -11858,22 +11848,22 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11881,36 +11871,44 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
         <v>21</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L157" s="12" t="inlineStr"/>
-      <c r="M157" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L157" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M157" s="12" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N157" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O157" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P157" s="13" t="n">
@@ -11920,22 +11918,22 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11943,7 +11941,7 @@
       </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G158" s="15" t="inlineStr">
@@ -11953,34 +11951,34 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>21</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M158" s="15" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N158" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O158" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P158" s="16" t="n">
@@ -12005,7 +12003,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -12039,7 +12037,7 @@
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
@@ -12060,22 +12058,22 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-17710</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Saint Lo] Migration</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>Saint Lo</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12083,40 +12081,28 @@
       </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G160" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G160" s="15" t="inlineStr"/>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>25/11/2024</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L160" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28020</t>
-        </is>
-      </c>
-      <c r="M160" s="15" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L160" s="15" t="inlineStr"/>
+      <c r="M160" s="15" t="inlineStr"/>
       <c r="N160" s="16" t="n">
         <v>0</v>
       </c>
@@ -12130,22 +12116,22 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-17710</t>
+          <t>PDMDEP-16116</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[Saint Lo] Migration</t>
+          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Saint Lo</t>
+          <t>CD 01</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -12153,25 +12139,29 @@
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G161" s="12" t="inlineStr"/>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
       <c r="H161" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>25/11/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L161" s="12" t="inlineStr"/>
       <c r="M161" s="12" t="inlineStr"/>
@@ -12188,22 +12178,22 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16116</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>CD 01</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12226,11 +12216,11 @@
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K162" s="15" t="n">
         <v>0.5</v>
@@ -12250,22 +12240,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12288,14 +12278,14 @@
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J163" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L163" s="12" t="inlineStr"/>
       <c r="M163" s="12" t="inlineStr"/>
@@ -12312,22 +12302,22 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12350,14 +12340,14 @@
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
         <v>31</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L164" s="15" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -12374,22 +12364,22 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12412,14 +12402,14 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L165" s="12" t="inlineStr"/>
       <c r="M165" s="12" t="inlineStr"/>
@@ -12436,12 +12426,12 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
@@ -12451,7 +12441,7 @@
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12469,19 +12459,19 @@
       </c>
       <c r="H166" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J166" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -12498,22 +12488,22 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12536,14 +12526,14 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>1</v>
+        <v>3.58</v>
       </c>
       <c r="L167" s="12" t="inlineStr"/>
       <c r="M167" s="12" t="inlineStr"/>
@@ -12560,22 +12550,22 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12588,27 +12578,35 @@
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="L168" s="15" t="inlineStr"/>
-      <c r="M168" s="15" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L168" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M168" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N168" s="16" t="n">
         <v>0</v>
       </c>
@@ -12622,22 +12620,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12650,35 +12648,23 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H169" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H169" s="12" t="inlineStr"/>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
         <v>36</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L169" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M169" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L169" s="12" t="inlineStr"/>
+      <c r="M169" s="12" t="inlineStr"/>
       <c r="N169" s="13" t="n">
         <v>0</v>
       </c>
@@ -12692,12 +12678,12 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
@@ -12707,7 +12693,7 @@
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12723,20 +12709,32 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H170" s="15" t="inlineStr"/>
+      <c r="H170" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
         <v>36</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L170" s="15" t="inlineStr"/>
-      <c r="M170" s="15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L170" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M170" s="15" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N170" s="16" t="n">
         <v>0</v>
       </c>
@@ -12750,26 +12748,28 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD 14] Paramétrages</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
-        </is>
-      </c>
-      <c r="E171" s="12" t="n">
-        <v/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
@@ -12783,30 +12783,22 @@
       </c>
       <c r="H171" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
         <v>36</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L171" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M171" s="12" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L171" s="12" t="inlineStr"/>
+      <c r="M171" s="12" t="inlineStr"/>
       <c r="N171" s="13" t="n">
         <v>0</v>
       </c>
@@ -12820,27 +12812,23 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
-        </is>
-      </c>
-      <c r="C172" s="15" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C172" s="15" t="inlineStr"/>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E172" s="15" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F172" s="15" t="inlineStr">
@@ -12855,19 +12843,19 @@
       </c>
       <c r="H172" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
         <v>36</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>0.25</v>
+        <v>7</v>
       </c>
       <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -12884,25 +12872,21 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr"/>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E173" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="inlineStr"/>
       <c r="F173" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12910,52 +12894,52 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H173" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H173" s="12" t="inlineStr"/>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L173" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L173" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
       <c r="M173" s="12" t="inlineStr"/>
       <c r="N173" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O173" s="13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P173" s="13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr"/>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E174" s="15" t="inlineStr"/>
@@ -12966,7 +12950,7 @@
       </c>
       <c r="G174" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H174" s="15" t="inlineStr"/>
@@ -12979,39 +12963,35 @@
         <v>2</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L174" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L174" s="15" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
       <c r="N174" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O174" s="16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P174" s="16" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr"/>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr"/>
@@ -13028,14 +13008,14 @@
       <c r="H175" s="12" t="inlineStr"/>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -13052,18 +13032,18 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr"/>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E176" s="15" t="inlineStr"/>
@@ -13074,23 +13054,31 @@
       </c>
       <c r="G176" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H176" s="15" t="inlineStr"/>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J176" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K176" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L176" s="15" t="inlineStr"/>
-      <c r="M176" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L176" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M176" s="15" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N176" s="16" t="n">
         <v>0</v>
       </c>
@@ -13104,18 +13092,18 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr"/>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr"/>
@@ -13126,31 +13114,23 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr"/>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L177" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M177" s="12" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L177" s="12" t="inlineStr"/>
+      <c r="M177" s="12" t="inlineStr"/>
       <c r="N177" s="13" t="n">
         <v>0</v>
       </c>
@@ -13164,18 +13144,18 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr"/>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr"/>
@@ -13186,23 +13166,31 @@
       </c>
       <c r="G178" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H178" s="15" t="inlineStr"/>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L178" s="15" t="inlineStr"/>
-      <c r="M178" s="15" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="L178" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M178" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N178" s="16" t="n">
         <v>0</v>
       </c>
@@ -13216,18 +13204,18 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1158</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE PLERIN</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr"/>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE PLERIN</t>
         </is>
       </c>
       <c r="E179" s="12" t="inlineStr"/>
@@ -13238,31 +13226,23 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr"/>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K179" s="12" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="L179" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M179" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L179" s="12" t="inlineStr"/>
+      <c r="M179" s="12" t="inlineStr"/>
       <c r="N179" s="13" t="n">
         <v>0</v>
       </c>
@@ -13276,18 +13256,18 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PSC-1158</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE PLERIN</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr"/>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE PLERIN</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E180" s="15" t="inlineStr"/>
@@ -13304,14 +13284,14 @@
       <c r="H180" s="15" t="inlineStr"/>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J180" s="15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L180" s="15" t="inlineStr"/>
       <c r="M180" s="15" t="inlineStr"/>
@@ -13328,18 +13308,18 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-668</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>VILLE DE DUGNY</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr"/>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>VILLE DE DUGNY</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr"/>
@@ -13356,11 +13336,11 @@
       <c r="H181" s="12" t="inlineStr"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="J181" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K181" s="12" t="n">
         <v>0.25</v>
@@ -13378,83 +13358,31 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="14" t="inlineStr">
-        <is>
-          <t>PSC-668</t>
-        </is>
-      </c>
-      <c r="B182" s="15" t="inlineStr">
-        <is>
-          <t>VILLE DE DUGNY</t>
-        </is>
-      </c>
-      <c r="C182" s="15" t="inlineStr"/>
-      <c r="D182" s="15" t="inlineStr">
-        <is>
-          <t>VILLE DE DUGNY</t>
-        </is>
-      </c>
-      <c r="E182" s="15" t="inlineStr"/>
-      <c r="F182" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G182" s="15" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H182" s="15" t="inlineStr"/>
-      <c r="I182" s="15" t="inlineStr">
-        <is>
-          <t>04/04/2025</t>
-        </is>
-      </c>
-      <c r="J182" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K182" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L182" s="15" t="inlineStr"/>
-      <c r="M182" s="15" t="inlineStr"/>
-      <c r="N182" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="18" t="inlineStr">
+      <c r="A182" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B183" s="18" t="inlineStr"/>
-      <c r="C183" s="18" t="inlineStr"/>
-      <c r="D183" s="18" t="inlineStr"/>
-      <c r="E183" s="18" t="inlineStr"/>
-      <c r="F183" s="18" t="inlineStr"/>
-      <c r="G183" s="18" t="inlineStr"/>
-      <c r="H183" s="18" t="inlineStr"/>
-      <c r="I183" s="18" t="inlineStr"/>
-      <c r="J183" s="18" t="inlineStr"/>
-      <c r="K183" s="18" t="inlineStr"/>
-      <c r="L183" s="18" t="inlineStr"/>
-      <c r="M183" s="18" t="inlineStr"/>
-      <c r="N183" s="19" t="n">
-        <v>47211.266</v>
-      </c>
-      <c r="O183" s="19" t="n">
+      <c r="B182" s="18" t="inlineStr"/>
+      <c r="C182" s="18" t="inlineStr"/>
+      <c r="D182" s="18" t="inlineStr"/>
+      <c r="E182" s="18" t="inlineStr"/>
+      <c r="F182" s="18" t="inlineStr"/>
+      <c r="G182" s="18" t="inlineStr"/>
+      <c r="H182" s="18" t="inlineStr"/>
+      <c r="I182" s="18" t="inlineStr"/>
+      <c r="J182" s="18" t="inlineStr"/>
+      <c r="K182" s="18" t="inlineStr"/>
+      <c r="L182" s="18" t="inlineStr"/>
+      <c r="M182" s="18" t="inlineStr"/>
+      <c r="N182" s="19" t="n">
+        <v>44196.716</v>
+      </c>
+      <c r="O182" s="19" t="n">
         <v>51747.57799999999</v>
       </c>
-      <c r="P183" s="19" t="n">
-        <v>180.42</v>
+      <c r="P182" s="19" t="n">
+        <v>175.52</v>
       </c>
     </row>
   </sheetData>
@@ -13637,7 +13565,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13649,7 +13576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -13675,7 +13602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 12 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 13 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -14005,22 +13932,18 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
-        </is>
-      </c>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr"/>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -14035,7 +13958,7 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
@@ -14043,37 +13966,33 @@
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34638</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>00176478</t>
-        </is>
-      </c>
+          <t>PDMDEP-35904</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr"/>
       <c r="K10" s="16" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34613</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE FORT-DE-FRANCE] - Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FORT-DE-FRANCE</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -14088,7 +14007,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="H11" s="12" t="n">
@@ -14096,37 +14015,37 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34619</t>
+          <t>PDMDEP-34638</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>00176429</t>
+          <t>00176478</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>3260</v>
+        <v>815</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34613</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t>[COMMUNE DE FORT-DE-FRANCE] - Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE FORT-DE-FRANCE</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t>Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -14141,7 +14060,7 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
@@ -14149,37 +14068,37 @@
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34587</t>
+          <t>PDMDEP-34619</t>
         </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>00176129</t>
+          <t>00176429</t>
         </is>
       </c>
       <c r="K12" s="16" t="n">
-        <v>815</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -14202,12 +14121,12 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34088</t>
+          <t>PDMDEP-34587</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>00170725</t>
+          <t>00176129</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
@@ -14217,22 +14136,22 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -14247,7 +14166,7 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
@@ -14255,12 +14174,12 @@
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33507</t>
+          <t>PDMDEP-34088</t>
         </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>00168118</t>
+          <t>00170725</t>
         </is>
       </c>
       <c r="K14" s="16" t="n">
@@ -14270,22 +14189,22 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -14300,7 +14219,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="H15" s="12" t="n">
@@ -14308,12 +14227,12 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33019</t>
+          <t>PDMDEP-33507</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>00165370</t>
+          <t>00168118</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
@@ -14323,22 +14242,22 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32950</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 1/2</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -14361,12 +14280,12 @@
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32956</t>
+          <t>PDMDEP-33019</t>
         </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>00165250</t>
+          <t>00165370</t>
         </is>
       </c>
       <c r="K16" s="16" t="n">
@@ -14374,21 +14293,74 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32950</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DU PONTET</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Migration GeODP Placier 1/2</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32956</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>00165250</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr"/>
-      <c r="C17" s="18" t="inlineStr"/>
-      <c r="D17" s="18" t="inlineStr"/>
-      <c r="E17" s="18" t="inlineStr"/>
-      <c r="F17" s="18" t="inlineStr"/>
-      <c r="G17" s="18" t="inlineStr"/>
-      <c r="H17" s="18" t="inlineStr"/>
-      <c r="I17" s="18" t="inlineStr"/>
-      <c r="J17" s="18" t="inlineStr"/>
-      <c r="K17" s="19" t="n">
+      <c r="B18" s="18" t="inlineStr"/>
+      <c r="C18" s="18" t="inlineStr"/>
+      <c r="D18" s="18" t="inlineStr"/>
+      <c r="E18" s="18" t="inlineStr"/>
+      <c r="F18" s="18" t="inlineStr"/>
+      <c r="G18" s="18" t="inlineStr"/>
+      <c r="H18" s="18" t="inlineStr"/>
+      <c r="I18" s="18" t="inlineStr"/>
+      <c r="J18" s="18" t="inlineStr"/>
+      <c r="K18" s="19" t="n">
         <v>12225</v>
       </c>
     </row>
@@ -14407,6 +14379,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14881,26 +14854,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>147.42</v>
+        <v>151.17</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>48.92</v>
+        <v>49.17</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>19.25</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>215.58</v>
+        <v>219.58</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>30.17</v>
+        <v>30.92</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>427.88</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14884,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>0</v>
@@ -14920,7 +14893,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>7.5</v>
@@ -14930,7 +14903,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.9%</t>
         </is>
       </c>
     </row>
@@ -14942,7 +14915,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>103.25</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -15106,7 +15079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15130,7 +15103,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 27 commande(s)</t>
+          <t>Épics créées ce mois — 28 commande(s)</t>
         </is>
       </c>
     </row>
@@ -15185,22 +15158,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35672</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35666</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -15220,32 +15193,32 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00181382</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>28915.01</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35636</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35627</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANNEMASSE</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -15265,32 +15238,32 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00181182</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
-        <v>9264</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -15303,39 +15276,35 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G7" s="15" t="inlineStr"/>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180831</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>1200</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35672</t>
+          <t>PDMDEP-35587</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35666</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -15345,7 +15314,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -15355,32 +15324,32 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00181382</t>
+          <t>00180931</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
+          <t>PDMDEP-35606</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -15393,35 +15362,39 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr"/>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00180831</t>
+          <t>00181049</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35733</t>
+          <t>PDMDEP-35636</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35727</t>
+          <t>PDMDEP-35627</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIEUX BOUCAU</t>
+          <t>COMMUNE D'ANNEMASSE</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -15441,32 +15414,32 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00181531</t>
+          <t>00181182</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>4815</v>
+        <v>9264</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35747</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35743</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -15476,7 +15449,7 @@
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -15486,32 +15459,32 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>00181626</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35606</t>
+          <t>PDMDEP-35733</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35597</t>
+          <t>PDMDEP-35727</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE VIEUX BOUCAU</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -15531,22 +15504,22 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>00181049</t>
+          <t>00181531</t>
         </is>
       </c>
       <c r="I12" s="27" t="n">
-        <v>0</v>
+        <v>4815</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35758</t>
+          <t>PDMDEP-35747</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35752</t>
+          <t>PDMDEP-35743</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -15556,7 +15529,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>COMMUNE D'EYSINES</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -15576,32 +15549,32 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>00181622</t>
+          <t>00181626</t>
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>4900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -15621,11 +15594,11 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I14" s="27" t="n">
-        <v>6285</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="15">
@@ -15766,22 +15739,22 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35587</t>
+          <t>PDMDEP-35758</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35583</t>
+          <t>PDMDEP-35752</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -15801,32 +15774,32 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>00180931</t>
+          <t>00181622</t>
         </is>
       </c>
       <c r="I18" s="27" t="n">
-        <v>0</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35771</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35767</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -15846,11 +15819,11 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00181751</t>
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>455</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="20">
@@ -15901,22 +15874,22 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35464</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -15936,32 +15909,32 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00180631</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
-        <v>895</v>
+        <v>455</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35945</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35941</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>Commune de Dunkerque</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -15971,7 +15944,7 @@
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -15981,7 +15954,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00182674</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
@@ -15991,22 +15964,22 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35945</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35941</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Commune de Dunkerque</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -16016,7 +15989,7 @@
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -16026,7 +15999,7 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>00182674</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I23" s="26" t="n">
@@ -16036,22 +16009,22 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -16071,32 +16044,32 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>0</v>
+        <v>895</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35687</t>
+          <t>PDMDEP-35902</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35683</t>
+          <t>PDMDEP-35840</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -16109,39 +16082,35 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G25" s="15" t="inlineStr"/>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>00181396</t>
+          <t>00182109</t>
         </is>
       </c>
       <c r="I25" s="26" t="n">
-        <v>2333.33</v>
+        <v>895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35771</t>
+          <t>PDMDEP-35889</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35767</t>
+          <t>PDMDEP-35883</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA HAUTE SAVOIE (CD 74)</t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -16161,32 +16130,32 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>00181751</t>
+          <t>00182197</t>
         </is>
       </c>
       <c r="I26" s="27" t="n">
-        <v>2740</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35788</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35782</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -16206,32 +16175,32 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>00181845</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="I27" s="26" t="n">
-        <v>1412.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35889</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35883</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -16251,32 +16220,32 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>00182197</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="I28" s="27" t="n">
-        <v>5895</v>
+        <v>6382.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35902</t>
+          <t>PDMDEP-35687</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35840</t>
+          <t>PDMDEP-35683</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -16289,35 +16258,39 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G29" s="15" t="inlineStr"/>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>00182109</t>
+          <t>00181396</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>895</v>
+        <v>2333.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35788</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35782</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -16337,32 +16310,32 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00181845</t>
         </is>
       </c>
       <c r="I30" s="27" t="n">
-        <v>840</v>
+        <v>1412.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -16382,38 +16355,62 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>00181167</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>6382.5</v>
+        <v>840</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>27 commande(s)</t>
-        </is>
-      </c>
-      <c r="I32" s="25" t="n">
-        <v>97451</v>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-35957</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-35953</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DU CALVADOS (CD 14)</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>00182724</t>
+        </is>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B33" s="18" t="n"/>
@@ -16424,17 +16421,17 @@
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>13 commande(s)</t>
+          <t>28 commande(s)</t>
         </is>
       </c>
       <c r="I33" s="25" t="n">
-        <v>25822</v>
+        <v>97451</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B34" s="18" t="n"/>
@@ -16449,6 +16446,27 @@
         </is>
       </c>
       <c r="I34" s="25" t="n">
+        <v>25822</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>14 commande(s)</t>
+        </is>
+      </c>
+      <c r="I35" s="25" t="n">
         <v>71629</v>
       </c>
     </row>
